--- a/docs/数值表_v1.xlsx
+++ b/docs/数值表_v1.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" tabRatio="600" firstSheet="6" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-填写说明" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,36 +15,72 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-结局条件" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-部件池" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-待决问题" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9-本次修订" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="10">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <color rgb="FF0F1115"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="7">
@@ -57,27 +92,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="FF2F5597"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,23 +126,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </left>
       <right style="thin">
-        <color rgb="00B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </right>
       <top style="thin">
-        <color rgb="00B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,11 +163,41 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -495,14 +561,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>《试镜人生》数值表 v1</t>
@@ -526,21 +592,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. 只填【数值】列里状态为「待定」的黄色格子，其余列是给程序看的字段名，不要改。</t>
+          <t>1. 你已填完全部黄格子。本轮我把「待定」统一升级为「已定」，并修掉了 4 处内部矛盾。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2. 不确定的先留空，比拍一个错数好——空值我会在程序里报错提醒。</t>
+          <t>2. 改动清单见新增的 sheet「9-本次修订」，每条都写了为什么改。不同意的地方直接说，改回来很快。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3. 改完把这个 xlsx 丢回来即可，我会按字段名接进 Godot 的 Resource。</t>
+          <t>3. 你标记待确认的 sheet「7-部件池」映射表 —— 结论是【不需要那张表】，理由写在该页。</t>
         </is>
       </c>
     </row>
@@ -824,6 +890,431 @@
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>GDScript</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="68" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>本次修订（提提，Day 1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>只改了「数值表」，没动你的设计意图。下面每一条都给了理由，不同意的说一声就能改回去。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>改了什么</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>原值</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>改为</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2-经济收支 C5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PS5 总额 400</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>你填的每期金额是 135，分 3 期 = 405。原写 400 与分期对不上，按 135×3 校正了总额</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2-经济收支 C9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>逾期惩罚 = 状态下降</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>风评 −5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>「状态」不是属性名。状态栏只有 金钱/演技值/知名度/风评 四项，已改成能落地的具体数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4-公司条件表 全表</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>早期草案条件</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>已验证的实现</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>早期草案两条与代码不符：A 公司原为「录满 3 帧即可」（等于零条件，玩家在 A 学不到东西），现改为「全程无怒」承担教学关；C-2 / E-3 同步。这张表现在是代码的镜像</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5-知名度 黑红段</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>「黑红也是红（成就）」</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>「黑红也是红（微博标题）」</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GDD 范围边界写死「绝对不做成就」。原表标题仍是「成就」，与已定决策矛盾，已改并补上触发条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6-结局 龙套之王</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>投递次数≥10 且 演技≤5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>龙套档成功演出 ≥ 8 且 演技 ≤ 12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>「龙套之王」字面就是演过最多小角色的人，该用成功次数。演技上限必须 &gt; 演出次数否则数学上不可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6-结局 烂片女王</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>成功演出≥8 且 演技≤12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A/B 公司成功演出 ≥ 6 且 演技 ≤ 12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>★最重要的一条：改之前龙套之王和烂片女王描述的是同一件事（演得多 + 演技低），只是数字不同，玩家分不出区别。改为绑定 A/B 公司后，一个测「数量」一个测「品质」，两个维度才正交</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6-结局 被解雇</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>累计无成功投递≥8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>累计失败投递 ≥ 8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>「无成功投递」有歧义（天数还是次数）。已明确为失败次数，用 投递数−成功数 直接算得</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6-结局 欠债</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>（未定义）</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>金钱 &lt; 0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>原稿引用了「欠债未清」但全文没有定义。已定为金钱为负</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5-知名度</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>（未写清楚）</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>新增「知名度 = 结果档位 + 戏份档位」</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>本页同时存在「结果三档给知名度」和「戏份给知名度」两套值，没说是否叠加。已明确为相加</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7-部件池 映射表</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>结论：不需要独立映射表</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>公司的风格词（纯真/幻灭/反转）在实现里就是一组情绪条件，sheet 4 即映射表本身。详见 7 页</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>全表 状态列</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>你填过的格子统一升级为「已定」并染绿。现在全表只剩 sheet 8 的 4 条待定</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>新发现的问题（已写进各页校验，需要你拍板）</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>★ 行动点预算零冗余</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>投递12 + 上课3 + 打工6 = 21 点</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>刚好等于总行动点</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>三项全拉满就没有任何点留给随机事件。这是设计意图（逼玩家取舍），但要清楚它是零冗余的 —— 实测若发现事件几乎触发不了，优先降打工上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>★ 经济缺口是真实的</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A 公司 40 元 × 12 次 = 480</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3 周固定支出 645</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>纯靠 A 公司养不活自己，玩家必须往高档位走。这就是「演技投资」压力的来源，不是巧合 —— 但需要模拟器确认它没有紧到无解</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>★ E 公司主角可达但很紧</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>演技需 25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>最快第 3 周才够</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>影后要求「演过 E 公司主角」，而 E 门槛就是 25，等于第 3 周练满才够格，当周只剩 1 次投递额度容错。建议 Day 13 模拟器重点验这条</t>
         </is>
       </c>
     </row>
@@ -838,18 +1329,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>时间与行动点</t>
@@ -921,7 +1411,7 @@
           <t>天</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
@@ -951,12 +1441,12 @@
           <t>天</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>已定</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -977,12 +1467,12 @@
           <t>点</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>已定</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1003,7 +1493,7 @@
           <t>点</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
@@ -1033,7 +1523,7 @@
           <t>次</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
@@ -1063,12 +1553,12 @@
           <t>点</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>已定</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1089,12 +1579,12 @@
           <t>点</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>已定</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1115,12 +1605,12 @@
           <t>点</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>已定</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1141,7 +1631,7 @@
           <t>点</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
@@ -1163,9 +1653,9 @@
           <t>周数是否可加长</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>待定</t>
         </is>
@@ -1246,9 +1736,9 @@
           <t>打工</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>保底收入，与投递抢行动点</t>
@@ -1261,9 +1751,9 @@
           <t>表演课</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>演技投资，与投递抢行动点</t>
@@ -1276,9 +1766,9 @@
           <t>特殊事件</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t>随机的，不可控</t>
@@ -1291,10 +1781,132 @@
           <t>空闲</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>★ 校验：行动点预算刚好被周上限吃满</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>3周占用</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>投递试镜</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12 点</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4 次/周 × 3 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表演课</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3 点</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1 次/周 × 3 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>打工</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6 点</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2 次/周 × 3 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21 点</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>★ 正好等于总行动点 21 —— 零冗余</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>三项全拉满就没有任何行动点留给随机事件。这是设计意图（逼玩家取舍），但要清楚它是零冗余的</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>→ 随机事件永远在和投递抢行动点。若实测发现事件几乎触发不了，优先降 work_max_per_week 或 class_max_per_week。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1307,18 +1919,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>经济收支</t>
@@ -1382,20 +1993,22 @@
           <t>PS5费总额</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>405</v>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>整个游戏的核心目标</t>
+          <t>整个游戏的核心目标。★原填 400 与「135×3」对不上，已按 135×3 校正为 405</t>
         </is>
       </c>
     </row>
@@ -1410,15 +2023,17 @@
           <t>分期期数</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>期</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1438,18 +2053,20 @@
           <t>每期金额</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1462,15 +2079,17 @@
           <t>每期截止日</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>天</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1490,16 +2109,20 @@
           <t>逾期惩罚</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>风评 −5</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>状态下降？还是直接触发被解雇结局？</t>
+          <t>★原为「状态下降」，但「状态」不是属性名。已改为具体的 风评 −5</t>
         </is>
       </c>
     </row>
@@ -1514,15 +2137,17 @@
           <t>房租/周</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>80</v>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1542,15 +2167,17 @@
           <t>初始金钱</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>200</v>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1616,18 +2243,20 @@
           <t>打工收入/次</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="n">
+        <v>30</v>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1640,15 +2269,17 @@
           <t>打工每周限次</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>次</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1668,11 +2299,15 @@
           <t>打工是否影响知名度/风评</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1743,15 +2378,23 @@
           <t>最低</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D21" s="5">
+        <f>C21*2</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>C21*3</f>
+        <v/>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1764,15 +2407,23 @@
           <t>低</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="D22" s="5">
+        <f>C22*2</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
+        <f>C22*3</f>
+        <v/>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1785,15 +2436,23 @@
           <t>中</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D23" s="5">
+        <f>C23*2</f>
+        <v/>
+      </c>
+      <c r="E23" s="5">
+        <f>C23*3</f>
+        <v/>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1806,15 +2465,23 @@
           <t>中高</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="D24" s="5">
+        <f>C24*2</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
+        <f>C24*3</f>
+        <v/>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1827,15 +2494,23 @@
           <t>最高</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="D25" s="5">
+        <f>C25*2</f>
+        <v/>
+      </c>
+      <c r="E25" s="5">
+        <f>C25*3</f>
+        <v/>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1894,18 +2569,20 @@
           <t>表演课价格/次</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1918,18 +2595,20 @@
           <t>表演课 +演技值</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1942,18 +2621,20 @@
           <t>表演课每周限次</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
           <t>次</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1966,25 +2647,176 @@
           <t>经纪人礼物价格</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>砍掉</t>
+        </is>
+      </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>★好感已砍，这个礼物现在改为什么效果？见「8-待决问题」</t>
+          <t>好感系统已整体砍掉，此项一并砍掉；sheet 8 第 6 条据此关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>★ 校验（3 周现金流 —— 这决定「能不能活到结局」）</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3 周固定支出</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>645 元</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PS5 分期 405（135×3） + 房租 80×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3 周保底收入</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>380 元</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>初始 200 + 打工 30×6（2 次/周 × 3 周）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>必须靠片酬补的缺口</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>265 元</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>645 − 380</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>换算成 A 公司龙套</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7 次成功</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>★ 265 ÷ 40 ≈ 6.6 → 至少要 7 次成功投递，低于这个数必定中途破产</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>若三周表演课全上</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>缺口涨到 565</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>再多花 300 上课 → 需要 15 次 A 龙套，超过 12 次投递上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>★ 纯靠 A 公司养不活自己，必须往更高档次走 —— 这就是「演技投资」压力的真正来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>→ 缺口是真的：A 公司 40 元/次 × 12 次 = 480 &lt; 645。玩家被迫提升片酬档位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>→ 以上只保证「算得通」，尚未跑模拟器；Day 13 用 balance_sim.gd 复核。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -1994,18 +2826,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>演技值</t>
@@ -2069,15 +2900,17 @@
           <t>初始演技值</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2110,7 +2943,7 @@
           <t>文档</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2136,7 +2969,7 @@
           <t>文档</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2162,7 +2995,7 @@
           <t>文档</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2175,11 +3008,15 @@
           <t>投递失败是否给经验</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2199,11 +3036,15 @@
           <t>演技是否有衰减/上限</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2212,70 +3053,76 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>acting_cap</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>演技上限</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>点</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>公司演技门槛</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>门槛</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>校验</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A 烂片厂</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>文档</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>12次投递下可达</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>B 小公司</t>
+          <t>A 烂片厂</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -2284,136 +3131,135 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>★验证：初始若为0，只能靠表演课到3</t>
+          <t>12次投递下可达</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C 商业片</t>
+          <t>B 小公司</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>文档</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>★验证：初始若为0，只能靠表演课到3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>D 文艺片</t>
+          <t>C 商业片</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>文档</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>D 文艺片</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>E 大厂</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B19" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>文档</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>★验证：12次投递能否摸到25，需模拟</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>角色档位（同一公司内）</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>档位</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>演技要求</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>匹配线</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>龙套</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>文档</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>配角</t>
+          <t>龙套</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2421,35 +3267,196 @@
           <t>文档</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>配角</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>主角</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B25" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>文档</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>★主角要求的演技(15)高于C公司门槛(8)，需确认是否有意</t>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>★ 有意为之，不是笔误：主角要求 15 &gt; C 公司门槛 8，意味着在 C 公司得先演龙套/配角把演技练到 15 才能演主角。这是刻意的成长曲线</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>★ 校验（演技 ≥ 25 可达性 —— 影后与 E 公司门槛都要求 25）</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>动作</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>演技值</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>第 1 周</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>表演课 +3，龙套 ×3（+1）</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>第 2 周</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>表演课 +3，配角 ×3（+2）</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>第 3 周</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>表演课 +3，主角 ×2（+5）</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>28 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>行动点开销</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3 次上课 + 8 次投递 = 11 点</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>还剩 10 点可打工 / 事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>可达</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>★ 且第 3 周练到 25 之后，当周还剩 1 次投递额度，正好用来投 E 公司主角</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>上限对照</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>acting_cap = 30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>影后只要 25，留 5 点冗余；不会顶到天花板</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>→ 影后因此可达，但要求玩家三周都把钱和行动点压在演技上。交给模拟器复核这条紧不紧。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -2459,8 +3466,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2468,11 +3475,10 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>公司试镜条件表  ★核心★</t>
@@ -2510,7 +3516,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>各公司条件清单（待确认/待增补）</t>
+          <t>各公司条件清单 ★已与 tools/test_resolver.gd 对齐（该实现已通过 headless 验证）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -2522,120 +3528,96 @@
       <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>条件清单</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>演技门槛</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>难度层级</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>条件ID</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>条件描述</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>条件类型</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>A 烂片厂</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>L0 无要求</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>录满3帧即可通过</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>单值</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>建议</t>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>必选</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B 小公司</t>
+          <t>A 烂片厂</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>L1 单情绪</t>
+          <t>L0 情绪一致性</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>B-1</t>
+          <t>A-1</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>任一帧出现「喜」或「哀」</t>
+          <t>全程无「怒」</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>单值</t>
+          <t>NO_EMOTION(怒) = 0</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★一票否决</t>
         </is>
       </c>
     </row>
@@ -2650,70 +3632,62 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>L1 单情绪</t>
+          <t>L1 单情绪命中</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>B-2</t>
+          <t>B-1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>全程无「怒」</t>
+          <t>任一帧出现「喜」（≥1.0）</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>单值</t>
+          <t>HAS_EMOTION(喜)</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★一票否决</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C 商业片</t>
+          <t>B 小公司</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>L2 情绪纯度</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>B-2</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>「喜/纯真」为主导情绪</t>
+          <t>全程无「怒」</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>单值</t>
+          <t>NO_EMOTION(怒) = 0</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2731,65 +3705,57 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>C-2</t>
+          <t>C-1</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>无冲突情绪（怒/尬）</t>
+          <t>主导情绪为「喜」</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>单值</t>
+          <t>DOMINANT_EMOTION(喜)</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★一票否决</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>D 文艺片</t>
+          <t>C 商业片</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>L3 情绪曲线</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>C-2</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>情绪曲线呈递减（高→低，幻灭感）</t>
+          <t>平均情绪纯度 ≥ 0.55</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>结构</t>
+          <t>PURITY_MIN(0.55)</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2802,70 +3768,62 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>L3 情绪曲线</t>
+          <t>L3 曲线形态</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>末帧为「哀」或「尬」</t>
+          <t>效价曲线递减（幻灭感）</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>单值</t>
+          <t>VALENCE_TREND(递减)</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★一票否决</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>E 大厂</t>
+          <t>D 文艺片</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>L4 帧间反转</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>E-1</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>帧与帧之间发生情绪反转</t>
+          <t>末帧为「哀」</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>结构</t>
+          <t>LAST_FRAME_EMOTION(哀)</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2883,25 +3841,25 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>E-2</t>
+          <t>E-1</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>主导情绪纯度 ≥（待定）</t>
+          <t>帧间效价反转（幅度 ≥1.0）</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>单值</t>
+          <t>VALENCE_REVERSAL(1.0)</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>★一票否决</t>
         </is>
       </c>
     </row>
@@ -2914,41 +3872,57 @@
       <c r="B18" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>L4 帧间反转</t>
-        </is>
-      </c>
+      <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>E-3</t>
+          <t>E-2</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>末帧情绪与首帧相反</t>
+          <t>平均情绪纯度 ≥ 0.55</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>结构</t>
+          <t>PURITY_MIN(0.55)</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E 大厂</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>E-3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>全程无「怒」</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NO_EMOTION(怒) = 0</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>匹配度换算校验（按档位匹配线 30% / 50% / 70%）</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
@@ -2958,133 +3932,148 @@
       <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>总权重与匹配度换算（匹配线仍为 30% / 50% / 70%）</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>总权重</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>命中权重→匹配度</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>1/1 = 100%（无门槛，必过）</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>命中权重 → 匹配度</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>3</v>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>0/3=0% 1/3=33% 2/3=67% 3/3=100%</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>1/1 = 100%（唯一条件必过）</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>3</v>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
+          <t>0/3=0%   1/3=33%   2/3=67%   3/3=100%</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>3</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>0/4=0% 1/4=25% 2/4=50% 3/4=75% 4/4=100%</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0/4=0%   1/4=25%   2/4=50%   3/4=75%   4/4=100%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>★ 待你决定</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
@@ -3094,38 +4083,279 @@
       <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>条件清单是否采用上述「布尔条件 + 权重」方案</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>★ 难度分层实证（数据来自 test_resolver.gd）</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>每家公司要不要有「多个不同难度角色」共用同一套条件？</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>通过的公司（按龙套线 30%）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>是否允许同一公司有多个可投角色（龙套/配角/主角）分别对应不同条件？</t>
+          <t>全程喜（平坦）</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>A B C</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>喜→平→哀（滑落）</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>A B C D</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>喜→喜→哀（突转）</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>A B C E</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>喜+怒（杂情绪）</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>全空白（未拼装）</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>↑ 关键看点：滑落型只过 D 不过 E，突转型只过 E 不过 D —— L3/L4 确实互斥，五档分层成立。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>★ 一票否决（required）：关键条件不满足时匹配度直接归零，而不是按比例给分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   否则平坦型表情包能在 E 大厂拿到 50%（2/4），五档分层会被「部分给分」抹平。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>★ 本页已从早期草案换成上面这套已验证的实现，两处实质差异：</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1) A 公司原为「录满 3 帧即可」= 零条件，玩家在 A 学不到东西；现改为「全程无怒」，承担教学关职责。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2) C-2 从「无冲突情绪」改为「纯度 ≥0.55」；E-3 从「末帧与首帧相反」改为「全程无怒」（原 E-3 与 E-1 重复）。</t>
         </is>
       </c>
     </row>
@@ -3140,18 +4370,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>知名度 / 风评 / 负面曝光  （来自《试镜邮件与电子报反馈》docx）</t>
@@ -3215,15 +4444,17 @@
           <t>初始知名度</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3243,20 +4474,26 @@
           <t>初始风评</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>范围是-50~+50，0是中性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.6" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>fame_range</t>
@@ -3267,11 +4504,15 @@
           <t>知名度取值范围</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>0~100</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3291,11 +4532,15 @@
           <t>风评取值范围</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>负50到正50</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3315,15 +4560,17 @@
           <t>初始负面曝光累计</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3343,20 +4590,22 @@
           <t>播出延迟（投递成功→剧集播出）</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>天</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>★21天内必须很短，建议次日或当周末</t>
+          <t>本周所有投递的作品统一在本周末播出结算</t>
         </is>
       </c>
     </row>
@@ -3419,27 +4668,21 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>匹配度 ≥（待定）</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>+（待定）</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>+（待定）</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>不增加</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>匹配度 ≥70</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -3456,27 +4699,21 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>（待定）≤ 匹配度 &lt;（待定）</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>无明显变化</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>无明显变化</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>不增加</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>40≤ 匹配度 &lt;70</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -3493,27 +4730,21 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>匹配度 &lt;（待定）</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>+（待定）</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>-（待定）</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>+（待定）</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>匹配度 &lt;40</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3533,24 +4764,18 @@
           <t>低分 且 知名度 &lt; 门槛</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>无变化</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>无变化</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>不增加</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -3570,24 +4795,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>不自动增加</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>不自动下降</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>不计入个人</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>文档</t>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -3653,15 +4872,17 @@
           <t>标题开始直接点名玩家的门槛</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3681,15 +4902,17 @@
           <t>主角戏份知名度增量</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3709,15 +4932,17 @@
           <t>配角戏份知名度增量</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3737,15 +4962,17 @@
           <t>龙套戏份知名度增量</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -3765,11 +4992,15 @@
           <t>龙套表演进入新闻的条件</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>龙套 + 高分 + 知名度≥20</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -3789,11 +5020,15 @@
           <t>同一项目是否只结算一次</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -3801,15 +5036,36 @@
           <t>docx 明确待定</t>
         </is>
       </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>★ 知名度是两个来源相加（本页原先没写清楚）</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>黑红也是红（成就）</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
+          <t>来源一</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>结果档位</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>高分 +2 / 普通 +1 / 低分 +1（见上表）</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
@@ -3819,89 +5075,197 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>字段名</t>
+          <t>来源二</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>戏份档位</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
+          <t>主角 +3 / 配角 +2 / 龙套 +1</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>两者相加</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>一次「主角 + 高分」= +5；一次「龙套 + 高分」= +3</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>→ 点名门槛 20：约 4~7 次成功演出后，电子报开始直接写玩家名字。</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>黑红也是红（★不是成就系统，只是一条微博标题）</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>字段名</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>heihong_threshold</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>黑红成就累计门槛</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>触发门槛</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>docx 明确待定</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>负面曝光累计 ≥ 5 时，微博出现一条「黑红」类标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>heihong_metric</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>累计口径</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>负面曝光累计值 / 被点名吐槽次数</t>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>负面曝光累计值</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>低分演出每次 +1 负面曝光（见上表「低分」行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>heihong_effect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>仅一条微博标题</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>★GDD 范围边界写死「绝对不做成就」，所以这里只是标题，不是成就</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -3911,8 +5275,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3921,7 +5285,7 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>结局条件</t>
@@ -3931,7 +5295,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>★ 已按「投递上限12次」重写，等确认</t>
+          <t>★ 已按「投递上限12次」重写，并经本轮校对（两处改动见下方说明）</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -3970,8 +5334,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -3983,20 +5349,18 @@
           <t>演技 ≥ 25 且 演过 E 公司主角 且 凑齐 PS5 费</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>演技≥30，凑齐PS5费</t>
-        </is>
-      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -4008,20 +5372,18 @@
           <t>演技 ≥ 18 且 演过 D 公司主角</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>演技≥20，且演过D公司主角</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -4030,23 +5392,25 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>投递次数 ≥ 10 且 演技 ≤ 5</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>龙套档成功演出 ≥ 8 且 演技 ≤ 12</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>★已改</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>演技≤5，演出次数≥20（12次上限下不可达）</t>
+          <t>原「投递次数≥10 且 演技≤5」—— 见下方说明</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -4055,23 +5419,25 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>成功演出 ≥ 8 且 演技 ≤ 12</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>A/B 公司成功演出 ≥ 6 且 演技 ≤ 12</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>★已改</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>演技≤10，演出次数≥15（12次上限下不可达）</t>
+          <t>原「成功演出≥8 且 演技≤12」—— 见下方说明</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -4080,23 +5446,25 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>连续 7 天无成功投递 且 欠债未清</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>累计失败投递 ≥ 8 且 金钱 &lt; 0</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>多轮无戏 + 欠债</t>
+          <t>原 GDD「多轮无戏 + 欠债」</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>6</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -4108,21 +5476,21 @@
           <t>凑齐 PS5 费但未达上述任何一条</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>两者都不高，勉强凑齐</t>
+          <t>兜底结局</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>★ 关键校验：演技值是单调递增的</t>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>★ 本次改了什么、为什么</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -4134,77 +5502,224 @@
       <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>问题</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>「演出≥N」与「演技≤M」在 N&gt;M 时数学上互斥（低档角色每次成功 +1 演技）</t>
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>原填写</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>改为</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>理由</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>解法A（已采纳）</t>
+          <t>龙套之王</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>把「演出次数」定义为【投递次数】而非成功次数 → 投递多但失败多，演技自然低</t>
+          <t>投递次数≥10 且 演技≤5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>龙套档成功演出 ≥ 8 且 演技 ≤ 12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>「龙套之王」字面就是「演过最多小角色的人」，该用成功次数。演技上限从 5 提到 12，因为 8 次龙套成功必然带来 ≥8 点演技，写 ≤5 数学上不可达 —— 这正是原稿的死结</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>需确认</t>
+          <t>烂片女王</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>「烂片女王」「龙套之王」是否也应统一改成「投递次数」口径？</t>
+          <t>成功演出≥8 且 演技≤12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A/B 公司成功演出 ≥ 6 且 演技 ≤ 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>★最关键的一条：「烂片女王」的重点是「烂片」，不是「演得多」。改之前两个结局描述的是同一件事（演得多 + 演技低），只是数字不同，玩家分不出区别。改为绑定 A/B 公司后，龙套之王 = 数量，烂片女王 = 品质，两个维度才正交</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>被解雇</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>累计无成功投递≥8</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>累计失败投递 ≥ 8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>「无成功投递」有歧义（天数？次数？）。已明确为投递失败次数，可直接用 投递总数 − 成功数 算出，不需要新增状态</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>结局数量</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+          <t>欠债</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>（原文未定义）</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>金钱 &lt; 0</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>原稿引用了「欠债未清」但全文没有定义。已定为金钱为负 —— 房租/PS5 扣款扣不动时自然转负</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>GDD「必须做」只要求 1 个核心结局，「可以砍」里写了多余结局可以砍</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>当前草案保留 6 个 —— 请确认是要全做，还是先做 2~3 个</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>★ 关键校验：演技值是单调递增的</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>事实</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>低档角色每次成功至少 +1 演技，所以「成功演出 ≥ N」必然推出「演技 ≥ N」</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>推论</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>凡是要写「演技 ≤ M」的结局，M 必须 &gt; N，否则条件自相矛盾（原「龙套之王 演技≤5」就是这样死的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>本表检查</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>龙套之王 8 ≤ 12 ✓　烂片女王 6 ≤ 12 ✓　两个都成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>互斥性</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>龙套之王需 8 次龙套成功，烂片女王只需 6 次且可混配角 —— 两者可能同时成立，由优先级 3 &gt; 4 裁决</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>★ 结局数量</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GDD 要求</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>「必须做」只要求 1 个核心结局；「可以砍」里写了多余结局可砍</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>当前草案</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>保留 6 个 —— 尚未确认是全做还是先做 2~3 个（见 sheet 8）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -4214,17 +5729,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>表情部件池</t>
@@ -4286,9 +5800,9 @@
           <t>平静→睁大→瞪→含泪→眯笑</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>建议</t>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4311,9 +5825,9 @@
           <t>闭合→微张→大笑→撇嘴→发抖</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>建议</t>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4336,12 +5850,12 @@
           <t>舒展→上挑→紧锁→八字→斜挑</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -4357,9 +5871,9 @@
           <t>黑线/青筋/汗滴/泪珠/红晕/呆毛</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>建议</t>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -4377,13 +5891,13 @@
       <c r="B9" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4450,9 +5964,9 @@
           <t>帧</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>建议</t>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -4504,20 +6018,24 @@
           <t>每个部件打几个情绪标签</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>1~3</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>建议 1~3 个</t>
+          <t>多数部件 1 个主情绪 + 少量副情绪</t>
         </is>
       </c>
     </row>
@@ -4532,16 +6050,20 @@
           <t>情绪权重取值范围</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0 ~ 5</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>建议 1~5</t>
+          <t>已落到 PartData：六个 @export_range(0.0, 5.0, 0.1) 字段</t>
         </is>
       </c>
     </row>
@@ -4556,27 +6078,31 @@
           <t>帧级显示几个情绪标签给玩家</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>建议 top-2（隐藏公式下的唯一反馈出口）</t>
+          <t>top-2 —— 隐藏公式下玩家唯一的反馈出口</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>★ 注意：公司的偏好词与部件的情绪词不是同一套</t>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>★ 你标记待确认的那张「映射表」—— 结论：不需要</t>
         </is>
       </c>
       <c r="B19" s="3" t="n"/>
@@ -4590,48 +6116,147 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>部件用</t>
+          <t>问题</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>喜 / 怒 / 哀 / 惊 / 魅 / 尬（情绪）</t>
+          <t>公司偏好词（随便/喜/悲/纯真/幻灭/反转）与部件情绪词（喜/怒/哀/惊/魅/尬）不是同一套，是否要单独做一张映射表？</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>公司用</t>
+          <t>结论</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>随便 / 喜 / 悲 / 纯真 / 幻灭 / 反转（后三个是风格，不是情绪）</t>
+          <t>★ 不需要。判定引擎已经把公司条件直接写成「情绪向量上的判断」，纯真/幻灭/反转只是发给玩家看的风格名</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>必须补一张映射表</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>纯真=喜高哀低怒为0 / 幻灭=哀0.6+尬0.4 / 反转=帧间ΔE符号翻转</t>
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>公司偏好词</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>实际等价于</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>对应的条件</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>这张映射表也需要你确认</t>
+          <t>随便（A）</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>全程无「怒」</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NO_EMOTION(怒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>喜 / 悲（B）</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>任一帧出现「喜」+ 全程无「怒」</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HAS_EMOTION(喜) + NO_EMOTION(怒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>纯真（C）</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>主导情绪为「喜」+ 平均纯度 ≥0.55</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DOMINANT_EMOTION(喜) + PURITY_MIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>幻灭（D）</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>效价曲线递减 + 末帧为「哀」</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VALENCE_TREND(递减) + LAST_FRAME_EMOTION(哀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>反转（E）</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>帧间效价反转 + 纯度 ≥0.55 + 全程无「怒」</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VALENCE_REVERSAL + PURITY_MIN + NO_EMOTION(怒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>→ 「纯真 / 幻灭 / 反转」是发给玩家的风格词，不是新概念。它们在数据里就是上面那几行条件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>→ 所以 sheet 4 的条件清单 = 映射表本身。这张表已并入 sheet 4，本页不再单列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>→ 副作用：Boss 直聘上给玩家看的偏好词必须与 sheet 4 的描述一致，否则玩家永远猜不到。</t>
         </is>
       </c>
     </row>
@@ -4646,24 +6271,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="3" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>待决问题（读两份 docx 后新发现）</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -4782,12 +6405,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>建议：保持隐藏，只在黑红触发时可见，不上状态栏</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>【已定】负面曝光保持隐藏，只在「黑红」标题出现时可见，不上状态栏</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
     </row>
@@ -4807,12 +6430,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>建议：统一叫「知名度」，语义更清楚且 docx 已写死</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>【已定】统一叫「知名度」，两份 docx 已写死此名</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
     </row>
@@ -4832,12 +6455,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>建议：改为 +风评 或 解锁一次内定机会；也可以直接砍掉这项支出</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>待定</t>
+          <t>【已定】直接砍掉（好感系统已整体砍掉，此项失去存在意义）</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
     </row>
@@ -4905,12 +6528,12 @@
           <t>若能复用：在A公司（无门槛）录一次就能刷12次钱。若不能：3周要拼12次×3帧</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>【已定】表情包一次性消耗，每次投递都要重新拼装</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
@@ -4930,12 +6553,12 @@
           <t>GDD 说「立即看到结果」，但播出反馈在周末。到账点有两个选择</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>【已定】钱/演技值/知名度/风评全部在本周末结算，投递瞬间只出通过或失败</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
@@ -4955,12 +6578,12 @@
           <t>一周最多4次投递，4条标题各自弹窗会很碎</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>【已定】每周一期《有瓜有戏》，汇总本周所有播出标题</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
@@ -4980,17 +6603,116 @@
           <t>若一开始就有全部HR，Boss直聘就变成纯装饰</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>【已定】需先浏览过Boss直聘该公司页面，微信里才解锁对应HR</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>已定</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>★ 本轮新增的待决问题</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>冲突点</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>我的建议</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>随机事件没有行动点预算</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>投递12 + 上课3 + 打工6 = 21 点，刚好占满总行动点，随机事件只能从别处抢</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>先按现状做，Day 13 模拟器看事件实际触发率；太低就把打工上限降到 1 次/周</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6 个结局全做还是先做 2~3 个</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6 个结局的文案 + 判定是不小的工作量，而 M5 只剩 3 天</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>先做影后 / 龙套之王 / 平庸 三个（覆盖 好 / 坏 / 兜底），其余留占位</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="23" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/数值表_v1.xlsx
+++ b/docs/数值表_v1.xlsx
@@ -6271,7 +6271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6668,14 +6668,14 @@
           <t>投递12 + 上课3 + 打工6 = 21 点，刚好占满总行动点，随机事件只能从别处抢</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>先按现状做，Day 13 模拟器看事件实际触发率；太低就把打工上限降到 1 次/周</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>【已定】暂不单独给随机事件留预算，先按现状做（投递12+上课3+打工6=21 点占满）；Day 13 用模拟器实测随机事件触发率，太低就把打工上限降到 1 次/周</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
     </row>
@@ -6693,14 +6693,14 @@
           <t>6 个结局的文案 + 判定是不小的工作量，而 M5 只剩 3 天</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>先做影后 / 龙套之王 / 平庸 三个（覆盖 好 / 坏 / 兜底），其余留占位</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>待定</t>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>【已定】先做影后 / 龙套之王 / 平庸 三个（覆盖 好 / 坏 / 兜底），其余 3 个（文艺片女神 / 烂片女王 / 被解雇）留占位，M5 有余力再补</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>已定</t>
         </is>
       </c>
     </row>
@@ -6710,9 +6710,6 @@
     <row r="22">
       <c r="E22" s="23" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/数值表_v1.xlsx
+++ b/docs/数值表_v1.xlsx
@@ -83,7 +83,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +115,11 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -143,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,6 +200,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2826,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3193,17 +3207,17 @@
           <t>E 大厂</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>25</v>
+      <c r="B19" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>文档</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>★验证：12次投递能否摸到25，需模拟</t>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>✅ Day 2 已定 20：模拟器实测「可投递时刻的演技上限只有 21」，25 永远够不着（曾让影后整轮不可达）。详见第 37 行起</t>
         </is>
       </c>
     </row>
@@ -3316,9 +3330,9 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>★ 校验（演技 ≥ 25 可达性 —— 影后与 E 公司门槛都要求 25）</t>
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>（原推演 · ❌ 已推翻 → ✅ 已修复：E 门槛 25 改 20，见第 37 行起的「★ 复核」）</t>
         </is>
       </c>
       <c r="B27" s="3" t="n"/>
@@ -3414,14 +3428,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>结论</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>可达</t>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>❌ 不可达</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>原写「可达」，理由「第 3 周练到 25 之后当周还剩 1 次投递额度正好投 E 主角」——这句默认了演技**当周生效**。实际演技要到**周末结算**才兑现（决策 1.5），所以每一周之内演技是冻结的，「当周练到 25」这件事不存在</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3448,9 +3462,172 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>→ 影后因此可达，但要求玩家三周都把钱和行动点压在演技上。交给模拟器复核这条紧不紧。</t>
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>→ 结论：原推演作废（演技当周生效的假设不成立）。修复方案见第 37 行起。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>★ 复核（Day 2 · 数值模拟器实测）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>机制</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>演技的增量在**周末结算**时才兑现（决策 1.5）→ 每一周**之内**演技是冻结的</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>推论</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>一次投递能碰到的门槛上限 = 上一周结束时手上的演技 + 本周表演课那 3 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>第 1 周</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>表演课 +3，龙套 ×4（+1）→ 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>第 2 周</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>表演课 +3，配角 ×4（+2）→ 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>第 3 周</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>表演课 +3 → 21，然后这一周就结束了</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>天花板</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>E 门槛（已改）</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>25 → **20**（Day 2 拍板 A）—— 21 ≥ 20，进得去；且仍是五家里最高的（D 是 15）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>实测：门槛 25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>影后 0.0% ｜ 文艺片女神 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>实测：门槛 21</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>影后 100.0% ｜ 文艺片女神 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>实测：门槛 20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>影后 100.0%（推荐，留 1 点冗余）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>✅ 已采纳</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>E 门槛 25 → 20。只动一个数，其余设计一行不改。影后自身的条件「演技 ≥ 25」不变 —— 它在第 21 天结算之后才判，那时演技已到 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>影后自身的条件</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>「演技 ≥ 25」**不用改** —— 结局在第 21 天结算之后判，那时演技已经是 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>后续护栏</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>test_economy.gd 新增断言：**任何公司的演技门槛都不得超过「一周内能给到的演技上限」**（现为 21）—— 这个坑不会再被踩第二次</t>
         </is>
       </c>
     </row>
@@ -6287,6 +6464,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -6614,6 +6792,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6849,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>【已定】暂不单独给随机事件留预算，先按现状做（投递12+上课3+打工6=21 点占满）；Day 13 用模拟器实测随机事件触发率，太低就把打工上限降到 1 次/周</t>
+          <t>【已定】暂不单独给随机事件留预算，先按现状做（投递12+上课3+打工6=21 点占满）；Day 13 用模拟器实测随机事件触发率，太低就把打工上限降到 1 次/周 ｜ 【Day 2 补】实测已完成，见第 22 条：贪心玩家闲置 0.00 点</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -6705,10 +6884,54 @@
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="23" t="n"/>
+      <c r="A21" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>「影后」不可达：E 大厂演技门槛 25 够不着</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>E 门槛写 25（sheet 3 的「★ 校验」也按 25 推演，结论「可达」）。但演技要到周末结算才兑现（决策 5/10），每一周之内演技是冻结的 —— 玩家在**可投递时刻**的演技上限只有 21（7 → 18 → 21）。sheet 3 那句「第 3 周练到 25 之后当周还剩 1 次投递额度正好投 E 主角」默认了演技当周生效，与决策 10 冲突</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>【已定 · Day 2 拍板 A】E 公司演技门槛 25 → 20。模拟器实测：门槛 25 → 影后 0.0%；门槛 21 → 100%；门槛 20 → 100%。影后自身的条件「演技 ≥ 25」不用改 —— 它在第 21 天结算之后判，那时演技已是 30。另加护栏断言：任何公司门槛都不得超过「一周内能给到的演技上限」（21）</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="E22" s="23" t="n"/>
+      <c r="A22" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>随机事件到底占不占行动点</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>第 13 条当时的处置是「先按现状做，Day 13 用模拟器实测」。现在实测做完了：贪心玩家把 21 点压得**一点不剩**（投递 12 / 打工 6 / 上课 3 / 闲置 0.00）</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>【已定 · Day 5 拍板】事件占 **1 点**行动点（第 13 条与 sheet 1 的 ap_cost_event = 1 本来就写着「已定」，待决的只是「到底占不占」）。零冗余的代价**仍未决**：投递 12 + 上课 3 + 打工 6 正好 21 点，事件占点后玩家只能从投递或打工里让；唯一在谈的办法是把 work_max_per_week 从 2 降到 1（腾出 3 点），等事件内容到位、跑一遍模拟器看触发率再定（见进度.md 阻塞项 17）</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
